--- a/data/sample_summary/2026/6月/6月客户类型样本统计表.xlsx
+++ b/data/sample_summary/2026/6月/6月客户类型样本统计表.xlsx
@@ -590,7 +590,7 @@
         <v/>
       </c>
       <c r="F3" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
@@ -612,7 +612,7 @@
         <v/>
       </c>
       <c r="F4" s="4" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
@@ -634,7 +634,7 @@
         <v/>
       </c>
       <c r="F5" s="4" t="n">
-        <v>88</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
@@ -678,7 +678,7 @@
         <v/>
       </c>
       <c r="F7" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
@@ -700,7 +700,7 @@
         <v/>
       </c>
       <c r="F8" s="4" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
@@ -772,7 +772,7 @@
         <v/>
       </c>
       <c r="F11" s="4" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
@@ -794,7 +794,7 @@
         <v/>
       </c>
       <c r="F12" s="4" t="n">
-        <v>30</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
@@ -838,7 +838,7 @@
         <v/>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
@@ -910,7 +910,7 @@
         <v/>
       </c>
       <c r="F17" s="4" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
@@ -932,7 +932,7 @@
         <v/>
       </c>
       <c r="F18" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1">
@@ -1004,7 +1004,7 @@
         <v/>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1">
@@ -1026,7 +1026,7 @@
         <v/>
       </c>
       <c r="F22" s="4" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1">
@@ -1092,7 +1092,7 @@
         <v/>
       </c>
       <c r="F25" s="4" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1">
